--- a/results/all_resultsVip.xlsx
+++ b/results/all_resultsVip.xlsx
@@ -1,40 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuanVanThs\code\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\vrptw-for-pisso\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2499E2CE-2785-48A3-93EB-FE34C02E149C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBF0840-D4D4-406B-B0F1-4A1EB18F55B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>Instance</t>
   </si>
@@ -406,13 +392,19 @@
   </si>
   <si>
     <t>C2-N2</t>
+  </si>
+  <si>
+    <t>HCGA NV</t>
+  </si>
+  <si>
+    <t>HCGA TD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,6 +420,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -437,7 +435,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -445,17 +443,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -776,7 +794,7 @@
     <col min="17" max="17" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -804,19 +822,25 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
       <c r="P1" t="s">
         <v>122</v>
       </c>
       <c r="Q1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -861,8 +885,22 @@
         <f>C2-N2</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T2" s="4">
+        <v>10</v>
+      </c>
+      <c r="U2" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W2">
+        <f>B2-T2</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>C2-U2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -904,11 +942,25 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>C3-N3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q3:Q34" si="1">C3-N3</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>10</v>
+      </c>
+      <c r="U3" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W3">
+        <f t="shared" ref="W3:W57" si="2">B3-T3</f>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f t="shared" ref="X3:X57" si="3">C3-U3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -950,11 +1002,25 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>C4-N4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>10</v>
+      </c>
+      <c r="U4" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="3"/>
+        <v>-0.88000000000010914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -996,11 +1062,25 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>C5-N5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>10</v>
+      </c>
+      <c r="U5" s="3">
+        <v>852.43</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="3"/>
+        <v>-27.649999999999977</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -1042,11 +1122,25 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>C6-N6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>10</v>
+      </c>
+      <c r="U6" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1088,11 +1182,25 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>C7-N7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>10</v>
+      </c>
+      <c r="U7" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1134,11 +1242,25 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>C8-N8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>10</v>
+      </c>
+      <c r="U8" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1180,11 +1302,25 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>C9-N9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>10</v>
+      </c>
+      <c r="U9" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1226,11 +1362,25 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>C10-N10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>10</v>
+      </c>
+      <c r="U10" s="3">
+        <v>828.94</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1272,11 +1422,25 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>C11-N11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="4">
+        <v>3</v>
+      </c>
+      <c r="U11" s="3">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -1318,11 +1482,25 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>C12-N12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
+        <v>4</v>
+      </c>
+      <c r="U12" s="3">
+        <v>640.72</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="3"/>
+        <v>-49.160000000000082</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1364,11 +1542,25 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>C13-N13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>4</v>
+      </c>
+      <c r="U13" s="3">
+        <v>641.57000000000005</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="3"/>
+        <v>-50.400000000000091</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1410,11 +1602,25 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>C14-N14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
+        <v>650.07000000000005</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="3"/>
+        <v>-59.470000000000027</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1456,11 +1662,25 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>C15-N15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3">
+        <v>588.88</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1502,11 +1722,25 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>C16-N16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>3</v>
+      </c>
+      <c r="U16" s="3">
+        <v>588.49</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1548,11 +1782,25 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>C17-N17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3">
+        <v>588.29</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1594,11 +1842,25 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <f>C18-N18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
+        <v>588.32000000000005</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1639,12 +1901,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q19" s="2">
-        <f>C19-N19</f>
+      <c r="Q19" s="1">
+        <f t="shared" si="1"/>
         <v>-4.2000000000000455</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T19" s="4">
+        <v>19</v>
+      </c>
+      <c r="U19" s="4">
+        <v>1684.09</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="3"/>
+        <v>-37.490000000000009</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1685,12 +1961,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q20" s="2">
-        <f>C20-N20</f>
+      <c r="Q20" s="1">
+        <f t="shared" si="1"/>
         <v>-13.309999999999945</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T20" s="4">
+        <v>18</v>
+      </c>
+      <c r="U20" s="3">
+        <v>1506.9</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="3"/>
+        <v>-34.090000000000146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1731,12 +2021,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q21" s="2">
-        <f>C21-N21</f>
+      <c r="Q21" s="1">
+        <f t="shared" si="1"/>
         <v>-35.029999999999973</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T21" s="4">
+        <v>15</v>
+      </c>
+      <c r="U21" s="3">
+        <v>1282.67</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="3"/>
+        <v>-25.019999999999982</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1778,11 +2082,25 @@
         <v>3</v>
       </c>
       <c r="Q22">
-        <f>C22-N22</f>
+        <f t="shared" si="1"/>
         <v>10.190000000000055</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T22" s="4">
+        <v>12</v>
+      </c>
+      <c r="U22" s="3">
+        <v>1077.9100000000001</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="3"/>
+        <v>-60.410000000000082</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1824,11 +2142,25 @@
         <v>2</v>
       </c>
       <c r="Q23">
-        <f>C23-N23</f>
+        <f t="shared" si="1"/>
         <v>16.7800000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T23" s="4">
+        <v>16</v>
+      </c>
+      <c r="U23" s="3">
+        <v>1439.46</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="3"/>
+        <v>-45.569999999999936</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1870,11 +2202,25 @@
         <v>1</v>
       </c>
       <c r="Q24">
-        <f>C24-N24</f>
+        <f t="shared" si="1"/>
         <v>0.96000000000003638</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T24" s="4">
+        <v>13</v>
+      </c>
+      <c r="U24" s="3">
+        <v>1307.79</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="3"/>
+        <v>-54.799999999999955</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1915,12 +2261,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q25" s="2">
-        <f>C25-N25</f>
+      <c r="Q25" s="1">
+        <f t="shared" si="1"/>
         <v>-10.820000000000164</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T25" s="4">
+        <v>12</v>
+      </c>
+      <c r="U25" s="4">
+        <v>1210.02</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="3"/>
+        <v>-116.18000000000006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1961,12 +2321,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q26" s="2">
-        <f>C26-N26</f>
+      <c r="Q26" s="1">
+        <f t="shared" si="1"/>
         <v>-2.7799999999999727</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T26" s="4">
+        <v>10</v>
+      </c>
+      <c r="U26" s="3">
+        <v>999.12</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="3"/>
+        <v>-41.019999999999982</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -2007,12 +2381,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q27" s="2">
-        <f>C27-N27</f>
+      <c r="Q27" s="1">
+        <f t="shared" si="1"/>
         <v>-40.690000000000055</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T27" s="4">
+        <v>14</v>
+      </c>
+      <c r="U27" s="3">
+        <v>1272.8399999999999</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="3"/>
+        <v>-118.79999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -2054,11 +2442,25 @@
         <v>3</v>
       </c>
       <c r="Q28">
-        <f>C28-N28</f>
+        <f t="shared" si="1"/>
         <v>16.259999999999991</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T28" s="4">
+        <v>13</v>
+      </c>
+      <c r="U28" s="3">
+        <v>1177.21</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="3"/>
+        <v>-42.110000000000127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2099,12 +2501,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q29" s="2">
-        <f>C29-N29</f>
+      <c r="Q29" s="1">
+        <f t="shared" si="1"/>
         <v>-25.079999999999927</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T29" s="4">
+        <v>13</v>
+      </c>
+      <c r="U29" s="3">
+        <v>1169.22</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="3"/>
+        <v>-97.579999999999927</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -2146,11 +2562,25 @@
         <v>2</v>
       </c>
       <c r="Q30">
-        <f>C30-N30</f>
+        <f t="shared" si="1"/>
         <v>11.539999999999964</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T30" s="4">
+        <v>10</v>
+      </c>
+      <c r="U30" s="3">
+        <v>993.29</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="3"/>
+        <v>0.38999999999998636</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -2191,12 +2621,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q31" s="2">
-        <f>C31-N31</f>
+      <c r="Q31" s="1">
+        <f t="shared" si="1"/>
         <v>-62.629999999999882</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T31" s="4">
+        <v>4</v>
+      </c>
+      <c r="U31" s="3">
+        <v>1253.8800000000001</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="3"/>
+        <v>-64.1400000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -2237,12 +2681,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q32" s="2">
-        <f>C32-N32</f>
+      <c r="Q32" s="1">
+        <f t="shared" si="1"/>
         <v>-44.230000000000018</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T32" s="4">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
+        <v>1135.71</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <f t="shared" si="3"/>
+        <v>11.759999999999991</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2283,12 +2741,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q33" s="2">
-        <f>C33-N33</f>
+      <c r="Q33" s="1">
+        <f t="shared" si="1"/>
         <v>-28.740000000000009</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T33" s="4">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3">
+        <v>962.98</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="3"/>
+        <v>-52.220000000000027</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -2329,12 +2801,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q34" s="2">
-        <f>C34-N34</f>
+      <c r="Q34" s="1">
+        <f t="shared" si="1"/>
         <v>-50.669999999999959</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T34" s="4">
+        <v>6</v>
+      </c>
+      <c r="U34" s="3">
+        <v>768.33</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="X34">
+        <f t="shared" si="3"/>
+        <v>6.5199999999999818</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -2376,11 +2862,25 @@
         <v>1</v>
       </c>
       <c r="Q35">
-        <f>C35-N35</f>
+        <f t="shared" ref="Q35:Q57" si="4">C35-N35</f>
         <v>3.8000000000000682</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T35" s="4">
+        <v>4</v>
+      </c>
+      <c r="U35" s="3">
+        <v>1025.97</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <f t="shared" si="3"/>
+        <v>-27.740000000000009</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -2422,11 +2922,25 @@
         <v>1</v>
       </c>
       <c r="Q36">
-        <f>C36-N36</f>
+        <f t="shared" si="4"/>
         <v>44.82000000000005</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T36" s="4">
+        <v>5</v>
+      </c>
+      <c r="U36" s="3">
+        <v>976.28</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X36">
+        <f t="shared" si="3"/>
+        <v>-25.319999999999936</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -2467,12 +2981,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q37" s="2">
-        <f>C37-N37</f>
+      <c r="Q37" s="1">
+        <f t="shared" si="4"/>
         <v>-38.720000000000027</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T37" s="4">
+        <v>5</v>
+      </c>
+      <c r="U37" s="3">
+        <v>874.32</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X37">
+        <f t="shared" si="3"/>
+        <v>-22.430000000000064</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -2514,11 +3042,25 @@
         <v>1</v>
       </c>
       <c r="Q38">
-        <f>C38-N38</f>
+        <f t="shared" si="4"/>
         <v>10.739999999999895</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T38" s="4">
+        <v>3</v>
+      </c>
+      <c r="U38" s="3">
+        <v>742.84</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <f t="shared" si="3"/>
+        <v>-5.2800000000000864</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -2559,12 +3101,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q39" s="2">
-        <f>C39-N39</f>
+      <c r="Q39" s="1">
+        <f t="shared" si="4"/>
         <v>-4.8199999999999363</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T39" s="4">
+        <v>5</v>
+      </c>
+      <c r="U39" s="3">
+        <v>922.09</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X39">
+        <f t="shared" si="3"/>
+        <v>-17.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -2605,12 +3161,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q40" s="3">
-        <f>C40-N40</f>
+      <c r="Q40">
+        <f t="shared" si="4"/>
         <v>25.299999999999955</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T40" s="4">
+        <v>6</v>
+      </c>
+      <c r="U40" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="X40">
+        <f t="shared" si="3"/>
+        <v>-13.230000000000018</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -2651,12 +3221,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q41" s="2">
-        <f>C41-N41</f>
+      <c r="Q41" s="1">
+        <f t="shared" si="4"/>
         <v>-112.25999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T41" s="4">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3">
+        <v>795.96</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <f t="shared" si="3"/>
+        <v>-22.509999999999991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -2697,12 +3281,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q42" s="2">
-        <f>C42-N42</f>
+      <c r="Q42" s="1">
+        <f t="shared" si="4"/>
         <v>-27.700000000000045</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T42" s="4">
+        <v>16</v>
+      </c>
+      <c r="U42" s="3">
+        <v>1684.99</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <f t="shared" si="3"/>
+        <v>-15.740000000000009</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2743,12 +3341,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q43" s="2">
-        <f>C43-N43</f>
+      <c r="Q43" s="1">
+        <f t="shared" si="4"/>
         <v>-61.6400000000001</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T43" s="4">
+        <v>13</v>
+      </c>
+      <c r="U43" s="3">
+        <v>1523.19</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="X43">
+        <f t="shared" si="3"/>
+        <v>-30.080000000000155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -2790,11 +3402,25 @@
         <v>1</v>
       </c>
       <c r="Q44">
-        <f>C44-N44</f>
+        <f t="shared" si="4"/>
         <v>80.819999999999936</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T44" s="4">
+        <v>12</v>
+      </c>
+      <c r="U44" s="4">
+        <v>1370.1</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <f t="shared" si="3"/>
+        <v>-27.6099999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2836,11 +3462,25 @@
         <v>1</v>
       </c>
       <c r="Q45">
-        <f>C45-N45</f>
+        <f t="shared" si="4"/>
         <v>15.670000000000073</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T45" s="4">
+        <v>11</v>
+      </c>
+      <c r="U45" s="3">
+        <v>1234.27</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <f t="shared" si="3"/>
+        <v>-83.119999999999891</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2881,12 +3521,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q46" s="2">
-        <f>C46-N46</f>
+      <c r="Q46" s="1">
+        <f t="shared" si="4"/>
         <v>-48.25</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T46" s="4">
+        <v>14</v>
+      </c>
+      <c r="U46" s="3">
+        <v>1601.86</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="X46">
+        <f t="shared" si="3"/>
+        <v>-20.669999999999845</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -2928,11 +3582,25 @@
         <v>3</v>
       </c>
       <c r="Q47">
-        <f>C47-N47</f>
+        <f t="shared" si="4"/>
         <v>4.4800000000000182</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T47" s="4">
+        <v>14</v>
+      </c>
+      <c r="U47" s="3">
+        <v>1448.6</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <f t="shared" si="3"/>
+        <v>-19.389999999999873</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -2974,11 +3642,25 @@
         <v>1</v>
       </c>
       <c r="Q48">
-        <f>C48-N48</f>
+        <f t="shared" si="4"/>
         <v>38.619999999999891</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T48" s="4">
+        <v>12</v>
+      </c>
+      <c r="U48" s="3">
+        <v>1285.9100000000001</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <f t="shared" si="3"/>
+        <v>-16.810000000000173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>41</v>
       </c>
@@ -3020,57 +3702,85 @@
         <v>1</v>
       </c>
       <c r="Q49">
-        <f>C49-N49</f>
+        <f t="shared" si="4"/>
         <v>19.029999999999973</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="T49" s="4">
+        <v>11</v>
+      </c>
+      <c r="U49" s="3">
+        <v>1186.42</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <f t="shared" si="3"/>
+        <v>-27.570000000000164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>6</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="1">
         <v>1338.49</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>2572.4699999999998</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="1">
         <v>163</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>896.84</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="1">
         <v>400</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>96</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="1">
         <v>621.1</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M50" s="1">
         <v>4</v>
       </c>
-      <c r="N50" s="2">
+      <c r="N50" s="1">
         <v>1406.94</v>
       </c>
-      <c r="P50" s="2">
+      <c r="P50" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q50" s="2">
-        <f>C50-N50</f>
+      <c r="Q50" s="1">
+        <f t="shared" si="4"/>
         <v>-68.450000000000045</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T50" s="4">
+        <v>8</v>
+      </c>
+      <c r="U50" s="4">
+        <v>1383.07</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="X50">
+        <f t="shared" si="3"/>
+        <v>-44.579999999999927</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>43</v>
       </c>
@@ -3111,12 +3821,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q51" s="2">
-        <f>C51-N51</f>
+      <c r="Q51" s="1">
+        <f t="shared" si="4"/>
         <v>-194.75</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T51" s="4">
+        <v>10</v>
+      </c>
+      <c r="U51" s="3">
+        <v>1167.69</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="X51">
+        <f t="shared" si="3"/>
+        <v>3.2100000000000364</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -3157,12 +3881,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q52" s="2">
-        <f>C52-N52</f>
+      <c r="Q52" s="1">
+        <f t="shared" si="4"/>
         <v>-83.949999999999932</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T52" s="4">
+        <v>6</v>
+      </c>
+      <c r="U52" s="3">
+        <v>962.6</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X52">
+        <f t="shared" si="3"/>
+        <v>3.0699999999999363</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -3203,12 +3941,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q53" s="3">
-        <f>C53-N53</f>
+      <c r="Q53">
+        <f t="shared" si="4"/>
         <v>7.1699999999999591</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T53" s="4">
+        <v>5</v>
+      </c>
+      <c r="U53" s="3">
+        <v>803.76</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="X53">
+        <f t="shared" si="3"/>
+        <v>1.8700000000000045</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -3249,12 +4001,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q54" s="2">
-        <f>C54-N54</f>
+      <c r="Q54" s="1">
+        <f t="shared" si="4"/>
         <v>-25.690000000000055</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T54" s="4">
+        <v>8</v>
+      </c>
+      <c r="U54" s="3">
+        <v>1302.3599999999999</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="X54">
+        <f t="shared" si="3"/>
+        <v>-30.399999999999864</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>47</v>
       </c>
@@ -3295,12 +4061,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q55" s="3">
-        <f>C55-N55</f>
+      <c r="Q55">
+        <f t="shared" si="4"/>
         <v>19.240000000000009</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T55" s="4">
+        <v>9</v>
+      </c>
+      <c r="U55" s="3">
+        <v>1211.6099999999999</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="2"/>
+        <v>-5</v>
+      </c>
+      <c r="X55">
+        <f t="shared" si="3"/>
+        <v>-46.049999999999955</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>48</v>
       </c>
@@ -3341,12 +4121,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q56" s="2">
-        <f>C56-N56</f>
+      <c r="Q56" s="1">
+        <f t="shared" si="4"/>
         <v>-34.580000000000155</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T56" s="4">
+        <v>7</v>
+      </c>
+      <c r="U56" s="3">
+        <v>1020.98</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="X56">
+        <f t="shared" si="3"/>
+        <v>5.5799999999999272</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>49</v>
       </c>
@@ -3387,9 +4181,23 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q57" s="2">
-        <f>C57-N57</f>
+      <c r="Q57" s="1">
+        <f t="shared" si="4"/>
         <v>-17.960000000000036</v>
+      </c>
+      <c r="T57" s="4">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3">
+        <v>813.47</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="X57">
+        <f t="shared" si="3"/>
+        <v>-3.2900000000000773</v>
       </c>
     </row>
   </sheetData>
